--- a/data/vendor-search/results_all_pet.xlsx
+++ b/data/vendor-search/results_all_pet.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,6 +492,11 @@
           <t>cpe:2.3:o:skymee:petalk_ai_firmware:3.2.2.30:*:*:*:*:*:*:*|cpe:2.3:h:skymee:petalk_ai:-:*:*:*:*:*:*:*|cpe:2.3:o:petwant:pf-103_firmware:4.22.2.42:*:*:*:*:*:*:*|cpe:2.3:h:petwant:pf-103:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>skymee</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +532,11 @@
           <t>cpe:2.3:o:skymee:petalk_ai_firmware:3.2.2.30:*:*:*:*:*:*:*|cpe:2.3:h:skymee:petalk_ai:-:*:*:*:*:*:*:*|cpe:2.3:o:petwant:pf-103_firmware:4.22.2.42:*:*:*:*:*:*:*|cpe:2.3:h:petwant:pf-103:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>skymee</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,6 +572,11 @@
           <t>cpe:2.3:o:skymee:petalk_ai_firmware:3.2.2.30:*:*:*:*:*:*:*|cpe:2.3:h:skymee:petalk_ai:-:*:*:*:*:*:*:*|cpe:2.3:o:petwant:pf-103_firmware:4.22.2.42:*:*:*:*:*:*:*|cpe:2.3:h:petwant:pf-103:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>skymee</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -592,6 +612,11 @@
           <t>cpe:2.3:o:skymee:petalk_ai_firmware:3.2.2.30:*:*:*:*:*:*:*|cpe:2.3:h:skymee:petalk_ai:-:*:*:*:*:*:*:*|cpe:2.3:o:petwant:pf-103_firmware:4.22.2.42:*:*:*:*:*:*:*|cpe:2.3:h:petwant:pf-103:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>skymee</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -627,6 +652,11 @@
           <t>cpe:2.3:o:skymee:petalk_ai_firmware:3.2.2.30:*:*:*:*:*:*:*|cpe:2.3:h:skymee:petalk_ai:-:*:*:*:*:*:*:*|cpe:2.3:o:petwant:pf-103_firmware:4.22.2.42:*:*:*:*:*:*:*|cpe:2.3:h:petwant:pf-103:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>skymee</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -662,6 +692,11 @@
           <t>cpe:2.3:o:skymee:petalk_ai_firmware:3.2.2.30:*:*:*:*:*:*:*|cpe:2.3:h:skymee:petalk_ai:-:*:*:*:*:*:*:*|cpe:2.3:o:petwant:pf-103_firmware:4.22.2.42:*:*:*:*:*:*:*|cpe:2.3:h:petwant:pf-103:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>skymee</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -697,6 +732,11 @@
           <t>cpe:2.3:o:skymee:petalk_ai_firmware:3.2.2.30:*:*:*:*:*:*:*|cpe:2.3:h:skymee:petalk_ai:-:*:*:*:*:*:*:*|cpe:2.3:o:petwant:pf-103_firmware:4.22.2.42:*:*:*:*:*:*:*|cpe:2.3:h:petwant:pf-103:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>skymee</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -732,6 +772,11 @@
           <t>cpe:2.3:o:skymee:petalk_ai_firmware:3.2.2.30:*:*:*:*:*:*:*|cpe:2.3:h:skymee:petalk_ai:-:*:*:*:*:*:*:*|cpe:2.3:o:petwant:pf-103_firmware:4.22.2.42:*:*:*:*:*:*:*|cpe:2.3:h:petwant:pf-103:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>skymee</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -767,6 +812,11 @@
           <t>cpe:2.3:o:skymee:petalk_ai_firmware:3.2.2.30:*:*:*:*:*:*:*|cpe:2.3:h:skymee:petalk_ai:-:*:*:*:*:*:*:*|cpe:2.3:o:petwant:pf-103_firmware:4.22.2.42:*:*:*:*:*:*:*|cpe:2.3:h:petwant:pf-103:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>skymee</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -802,6 +852,11 @@
           <t>cpe:2.3:a:ambarella:oryx_rtsp_server:2020-01-07:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>furbo|furbo dog camera</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -837,6 +892,11 @@
           <t>cpe:2.3:o:furbo:dog_camera_firmware:542:*:*:*:*:*:*:*|cpe:2.3:h:furbo:dog_camera:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>furbo|furbo dog camera</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -872,6 +932,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -907,6 +972,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -942,6 +1012,11 @@
           <t>cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -977,6 +1052,11 @@
           <t>cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1012,6 +1092,11 @@
           <t>cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1047,6 +1132,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1082,6 +1172,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1117,6 +1212,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1152,6 +1252,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1187,6 +1292,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1222,6 +1332,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1257,6 +1372,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1288,6 +1408,11 @@
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1323,6 +1448,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1358,6 +1488,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1393,6 +1528,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1428,6 +1568,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1463,6 +1608,11 @@
           <t>cpe:2.3:o:furbo:furbo_mini_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_mini:-:*:*:*:*:*:*:*|cpe:2.3:o:furbo:furbo_360_dog_camera_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:furbo:furbo_360_dog_camera:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>furbo</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1498,6 +1648,11 @@
           <t>cpe:2.3:a:petlibro:petlibro:*:*:*:*:-:*:*:*</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>petlibro</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1533,6 +1688,11 @@
           <t>cpe:2.3:a:petlibro:petlibro:*:*:*:*:-:*:*:*</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>petlibro</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1568,6 +1728,11 @@
           <t>cpe:2.3:a:petlibro:petlibro:*:*:*:*:-:*:*:*</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>petlibro</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1603,6 +1768,11 @@
           <t>cpe:2.3:a:petlibro:petlibro:*:*:*:*:-:*:*:*</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>petlibro</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1638,6 +1808,11 @@
           <t>cpe:2.3:a:petlibro:petlibro:*:*:*:*:-:*:*:*</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>petlibro</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1671,6 +1846,11 @@
       <c r="G36" t="inlineStr">
         <is>
           <t>cpe:2.3:a:petlibro:petlibro:*:*:*:*:-:*:*:*</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>petlibro</t>
         </is>
       </c>
     </row>
